--- a/WpfUI/Resources/Templates/DotnetNetworking/TestCase/EnvRunDB.xlsx
+++ b/WpfUI/Resources/Templates/DotnetNetworking/TestCase/EnvRunDB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPTU\S1_SP25\CloneProject\RecordSolution_Nodejs\RecordApp\Resources\ProjectResource\DotNetWebbased\Question\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPTU\S1_SP25\CloneProject\RecordSolution_Nodejs\RecordApp\Resources\ProjectResource\DotNetWebbased\TestCase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DEE77E-2FE8-4AEB-9236-5A407BF599D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4030E23E-3804-4E1F-84DE-F48E651A8C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Step</t>
   </si>
@@ -33,20 +33,14 @@
     <t>Keyword action</t>
   </si>
   <si>
-    <t>generate_connection_file</t>
-  </si>
-  <si>
-    <t>copy_essential_files_and_folders</t>
-  </si>
-  <si>
-    <t>generate_database_script</t>
+    <t>reset_database</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,26 +59,20 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -101,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -110,12 +98,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -129,21 +146,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{216F6D8D-C489-4646-9558-334A5A65B940}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -154,6 +251,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{054913B0-5323-4F83-856A-AA921BB86A96}" name="Table1" displayName="Table1" ref="A1:B2" totalsRowShown="0" tableBorderDxfId="2">
+  <autoFilter ref="A1:B2" xr:uid="{054913B0-5323-4F83-856A-AA921BB86A96}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{EEF80A4C-AE1A-42E1-8D02-233D6645FC7A}" name="Step" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{1E0B1333-A75D-493C-BE3E-968ECB29CDD7}" name="Keyword action" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -473,47 +581,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57C292E-6388-4C7D-91A9-4D6083EF5987}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>